--- a/single_games_predictions/processed_match_predictions.xlsx
+++ b/single_games_predictions/processed_match_predictions.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Documents\Dokumente\Institut für Sportinformatik\WM Prognose 2026\Einzelspielprognosen\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1520C0-4F87-4575-9EA2-D1B6B6CD726F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
   <si>
     <t>Spiel_ID</t>
   </si>
@@ -61,15 +55,24 @@
     <t>deu_cuw</t>
   </si>
   <si>
+    <t>civ_deu</t>
+  </si>
+  <si>
     <t>Deutschland</t>
   </si>
   <si>
+    <t>Elfenbeinküste</t>
+  </si>
+  <si>
     <t>Curaçao</t>
   </si>
   <si>
     <t>14.06.2026</t>
   </si>
   <si>
+    <t>20.06.2026</t>
+  </si>
+  <si>
     <t>Heimsieg</t>
   </si>
   <si>
@@ -79,14 +82,14 @@
     <t>Heimniederlage</t>
   </si>
   <si>
-    <t>12.06.2026</t>
+    <t>17.06.2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,25 +148,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -201,7 +196,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -235,7 +230,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -270,10 +264,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -446,11 +439,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,21 +481,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -511,95 +504,209 @@
         <v>1.0443</v>
       </c>
       <c r="H2">
-        <v>0.91971199999999997</v>
+        <v>0.919712</v>
       </c>
       <c r="I2">
-        <v>91.971199999999996</v>
+        <v>91.9712</v>
       </c>
       <c r="J2">
-        <v>0.93770900000000001</v>
+        <v>0.937709</v>
       </c>
       <c r="K2">
-        <v>93.770899999999997</v>
+        <v>93.7709</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>7</v>
       </c>
       <c r="G3">
-        <v>17.428599999999999</v>
+        <v>17.4286</v>
       </c>
       <c r="H3">
-        <v>5.5107000000000003E-2</v>
+        <v>0.055107</v>
       </c>
       <c r="I3">
-        <v>5.5106999999999999</v>
+        <v>5.5107</v>
       </c>
       <c r="J3">
-        <v>4.5869E-2</v>
+        <v>0.045869</v>
       </c>
       <c r="K3">
         <v>4.5869</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>7</v>
       </c>
       <c r="G4">
-        <v>38.142899999999997</v>
+        <v>38.1429</v>
       </c>
       <c r="H4">
-        <v>2.5180000000000001E-2</v>
+        <v>0.02518</v>
       </c>
       <c r="I4">
-        <v>2.5179999999999998</v>
+        <v>2.518</v>
       </c>
       <c r="J4">
-        <v>1.6421999999999999E-2</v>
+        <v>0.016422</v>
       </c>
       <c r="K4">
-        <v>1.6422000000000001</v>
+        <v>1.6422</v>
       </c>
       <c r="L4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>1.5571</v>
+      </c>
+      <c r="H5">
+        <v>0.608775</v>
+      </c>
+      <c r="I5">
+        <v>60.8775</v>
+      </c>
+      <c r="J5">
+        <v>0.620015</v>
+      </c>
+      <c r="K5">
+        <v>62.0015</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>4.34</v>
+      </c>
+      <c r="H6">
+        <v>0.218422</v>
+      </c>
+      <c r="I6">
+        <v>21.8422</v>
+      </c>
+      <c r="J6">
+        <v>0.213693</v>
+      </c>
+      <c r="K6">
+        <v>21.3693</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>5.4857</v>
+      </c>
+      <c r="H7">
+        <v>0.172803</v>
+      </c>
+      <c r="I7">
+        <v>17.2803</v>
+      </c>
+      <c r="J7">
+        <v>0.166292</v>
+      </c>
+      <c r="K7">
+        <v>16.6292</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/single_games_predictions/processed_match_predictions.xlsx
+++ b/single_games_predictions/processed_match_predictions.xlsx
@@ -82,7 +82,7 @@
     <t>Heimniederlage</t>
   </si>
   <si>
-    <t>17.06.2026</t>
+    <t>19.06.2026</t>
   </si>
 </sst>
 </file>
@@ -615,19 +615,19 @@
         <v>7</v>
       </c>
       <c r="G5">
-        <v>1.5571</v>
+        <v>1.5443</v>
       </c>
       <c r="H5">
-        <v>0.608775</v>
+        <v>0.616777</v>
       </c>
       <c r="I5">
-        <v>60.8775</v>
+        <v>61.6777</v>
       </c>
       <c r="J5">
-        <v>0.620015</v>
+        <v>0.627295</v>
       </c>
       <c r="K5">
-        <v>62.0015</v>
+        <v>62.7295</v>
       </c>
       <c r="L5" t="s">
         <v>22</v>
@@ -653,19 +653,19 @@
         <v>7</v>
       </c>
       <c r="G6">
-        <v>4.34</v>
+        <v>4.4114</v>
       </c>
       <c r="H6">
-        <v>0.218422</v>
+        <v>0.215912</v>
       </c>
       <c r="I6">
-        <v>21.8422</v>
+        <v>21.5912</v>
       </c>
       <c r="J6">
-        <v>0.213693</v>
+        <v>0.211517</v>
       </c>
       <c r="K6">
-        <v>21.3693</v>
+        <v>21.1517</v>
       </c>
       <c r="L6" t="s">
         <v>22</v>
@@ -691,19 +691,19 @@
         <v>7</v>
       </c>
       <c r="G7">
-        <v>5.4857</v>
+        <v>5.6929</v>
       </c>
       <c r="H7">
-        <v>0.172803</v>
+        <v>0.167311</v>
       </c>
       <c r="I7">
-        <v>17.2803</v>
+        <v>16.7311</v>
       </c>
       <c r="J7">
-        <v>0.166292</v>
+        <v>0.161187</v>
       </c>
       <c r="K7">
-        <v>16.6292</v>
+        <v>16.1187</v>
       </c>
       <c r="L7" t="s">
         <v>22</v>

--- a/single_games_predictions/processed_match_predictions.xlsx
+++ b/single_games_predictions/processed_match_predictions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
   <si>
     <t>Spiel_ID</t>
   </si>
@@ -58,12 +58,18 @@
     <t>civ_deu</t>
   </si>
   <si>
+    <t>ecu_deu</t>
+  </si>
+  <si>
     <t>Deutschland</t>
   </si>
   <si>
     <t>Elfenbeinküste</t>
   </si>
   <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
     <t>Curaçao</t>
   </si>
   <si>
@@ -73,6 +79,9 @@
     <t>20.06.2026</t>
   </si>
   <si>
+    <t>24.06.2026</t>
+  </si>
+  <si>
     <t>Heimsieg</t>
   </si>
   <si>
@@ -82,7 +91,7 @@
     <t>Heimniederlage</t>
   </si>
   <si>
-    <t>19.06.2026</t>
+    <t>23.06.2026</t>
   </si>
 </sst>
 </file>
@@ -440,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -486,16 +495,16 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -516,7 +525,7 @@
         <v>93.7709</v>
       </c>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -524,16 +533,16 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -554,7 +563,7 @@
         <v>4.5869</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -562,16 +571,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -592,7 +601,7 @@
         <v>1.6422</v>
       </c>
       <c r="L4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -600,16 +609,16 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>7</v>
@@ -630,7 +639,7 @@
         <v>62.7295</v>
       </c>
       <c r="L5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -638,16 +647,16 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -668,7 +677,7 @@
         <v>21.1517</v>
       </c>
       <c r="L6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -676,16 +685,16 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7">
         <v>7</v>
@@ -706,7 +715,121 @@
         <v>16.1187</v>
       </c>
       <c r="L7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>3.5771</v>
+      </c>
+      <c r="H8">
+        <v>0.264514</v>
+      </c>
+      <c r="I8">
+        <v>26.4514</v>
+      </c>
+      <c r="J8">
+        <v>0.261603</v>
+      </c>
+      <c r="K8">
+        <v>26.1603</v>
+      </c>
+      <c r="L8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9">
+        <v>3.87</v>
+      </c>
+      <c r="H9">
+        <v>0.244497</v>
+      </c>
+      <c r="I9">
+        <v>24.4497</v>
+      </c>
+      <c r="J9">
+        <v>0.240757</v>
+      </c>
+      <c r="K9">
+        <v>24.0757</v>
+      </c>
+      <c r="L9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>1.9271</v>
+      </c>
+      <c r="H10">
+        <v>0.490988</v>
+      </c>
+      <c r="I10">
+        <v>49.0988</v>
+      </c>
+      <c r="J10">
+        <v>0.49764</v>
+      </c>
+      <c r="K10">
+        <v>49.764</v>
+      </c>
+      <c r="L10" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/single_games_predictions/processed_match_predictions.xlsx
+++ b/single_games_predictions/processed_match_predictions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="30">
   <si>
     <t>Spiel_ID</t>
   </si>
@@ -61,6 +61,9 @@
     <t>ecu_deu</t>
   </si>
   <si>
+    <t>deu_par</t>
+  </si>
+  <si>
     <t>Deutschland</t>
   </si>
   <si>
@@ -73,6 +76,9 @@
     <t>Curaçao</t>
   </si>
   <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
     <t>14.06.2026</t>
   </si>
   <si>
@@ -91,13 +97,22 @@
     <t>Heimniederlage</t>
   </si>
   <si>
-    <t>23.06.2026</t>
+    <t>Heimteam qualifiziert</t>
+  </si>
+  <si>
+    <t>Gastteam qualifiziert</t>
+  </si>
+  <si>
+    <t>28.06.2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -150,11 +165,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -495,16 +511,16 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -525,7 +541,7 @@
         <v>93.7709</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -533,16 +549,16 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -563,7 +579,7 @@
         <v>4.5869</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -571,16 +587,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -601,7 +617,7 @@
         <v>1.6422</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -609,16 +625,16 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <v>7</v>
@@ -639,7 +655,7 @@
         <v>62.7295</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -647,16 +663,16 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -677,7 +693,7 @@
         <v>21.1517</v>
       </c>
       <c r="L6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -685,16 +701,16 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>7</v>
@@ -715,7 +731,7 @@
         <v>16.1187</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -723,16 +739,16 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -753,7 +769,7 @@
         <v>26.1603</v>
       </c>
       <c r="L8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -761,16 +777,16 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9">
         <v>7</v>
@@ -791,7 +807,7 @@
         <v>24.0757</v>
       </c>
       <c r="L9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -799,16 +815,16 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F10">
         <v>7</v>
@@ -829,7 +845,197 @@
         <v>49.764</v>
       </c>
       <c r="L10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2">
+        <v>46202</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+      <c r="G11">
+        <v>1.3714</v>
+      </c>
+      <c r="H11">
+        <v>0.694987</v>
+      </c>
+      <c r="I11">
+        <v>69.4987</v>
+      </c>
+      <c r="J11">
+        <v>0.708218</v>
+      </c>
+      <c r="K11">
+        <v>70.8218</v>
+      </c>
+      <c r="L11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="2">
+        <v>46202</v>
+      </c>
+      <c r="E12" t="s">
         <v>25</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12">
+        <v>4.9886</v>
+      </c>
+      <c r="H12">
+        <v>0.191062</v>
+      </c>
+      <c r="I12">
+        <v>19.1062</v>
+      </c>
+      <c r="J12">
+        <v>0.185747</v>
+      </c>
+      <c r="K12">
+        <v>18.5747</v>
+      </c>
+      <c r="L12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2">
+        <v>46202</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13">
+        <v>7</v>
+      </c>
+      <c r="G13">
+        <v>8.3643</v>
+      </c>
+      <c r="H13">
+        <v>0.113952</v>
+      </c>
+      <c r="I13">
+        <v>11.3952</v>
+      </c>
+      <c r="J13">
+        <v>0.106035</v>
+      </c>
+      <c r="K13">
+        <v>10.6035</v>
+      </c>
+      <c r="L13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="2">
+        <v>46202</v>
+      </c>
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>1.156</v>
+      </c>
+      <c r="H14">
+        <v>0.818695</v>
+      </c>
+      <c r="I14">
+        <v>81.8695</v>
+      </c>
+      <c r="J14">
+        <v>0.836741</v>
+      </c>
+      <c r="K14">
+        <v>83.6741</v>
+      </c>
+      <c r="L14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="2">
+        <v>46202</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>5.22</v>
+      </c>
+      <c r="H15">
+        <v>0.181305</v>
+      </c>
+      <c r="I15">
+        <v>18.1305</v>
+      </c>
+      <c r="J15">
+        <v>0.163259</v>
+      </c>
+      <c r="K15">
+        <v>16.3259</v>
+      </c>
+      <c r="L15" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/single_games_predictions/processed_match_predictions.xlsx
+++ b/single_games_predictions/processed_match_predictions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="42">
   <si>
     <t>Spiel_ID</t>
   </si>
@@ -64,6 +64,18 @@
     <t>deu_par</t>
   </si>
   <si>
+    <t>fra_mar</t>
+  </si>
+  <si>
+    <t>spa_bel</t>
+  </si>
+  <si>
+    <t>nor_eng</t>
+  </si>
+  <si>
+    <t>arg_sch</t>
+  </si>
+  <si>
     <t>Deutschland</t>
   </si>
   <si>
@@ -73,12 +85,36 @@
     <t>Ecuador</t>
   </si>
   <si>
+    <t>Frankreich</t>
+  </si>
+  <si>
+    <t>Spanien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norwegen </t>
+  </si>
+  <si>
+    <t>Argentinien</t>
+  </si>
+  <si>
     <t>Curaçao</t>
   </si>
   <si>
     <t>Paraguay</t>
   </si>
   <si>
+    <t>Marokko</t>
+  </si>
+  <si>
+    <t>Belgien</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>Schweiz</t>
+  </si>
+  <si>
     <t>14.06.2026</t>
   </si>
   <si>
@@ -103,7 +139,7 @@
     <t>Gastteam qualifiziert</t>
   </si>
   <si>
-    <t>28.06.2026</t>
+    <t>08.07.2026</t>
   </si>
 </sst>
 </file>
@@ -465,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -511,16 +547,16 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -541,7 +577,7 @@
         <v>93.7709</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -549,16 +585,16 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -579,7 +615,7 @@
         <v>4.5869</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -587,16 +623,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -617,7 +653,7 @@
         <v>1.6422</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -625,16 +661,16 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>7</v>
@@ -655,7 +691,7 @@
         <v>62.7295</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -663,16 +699,16 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -693,7 +729,7 @@
         <v>21.1517</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -701,16 +737,16 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F7">
         <v>7</v>
@@ -731,7 +767,7 @@
         <v>16.1187</v>
       </c>
       <c r="L7" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -739,16 +775,16 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -769,7 +805,7 @@
         <v>26.1603</v>
       </c>
       <c r="L8" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -777,16 +813,16 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F9">
         <v>7</v>
@@ -807,7 +843,7 @@
         <v>24.0757</v>
       </c>
       <c r="L9" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -815,16 +851,16 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F10">
         <v>7</v>
@@ -845,7 +881,7 @@
         <v>49.764</v>
       </c>
       <c r="L10" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -853,16 +889,16 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D11" s="2">
         <v>46202</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -883,7 +919,7 @@
         <v>70.8218</v>
       </c>
       <c r="L11" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -891,16 +927,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D12" s="2">
         <v>46202</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F12">
         <v>7</v>
@@ -921,7 +957,7 @@
         <v>18.5747</v>
       </c>
       <c r="L12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -929,16 +965,16 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D13" s="2">
         <v>46202</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F13">
         <v>7</v>
@@ -959,7 +995,7 @@
         <v>10.6035</v>
       </c>
       <c r="L13" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -967,16 +1003,16 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2">
         <v>46202</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -997,7 +1033,7 @@
         <v>83.6741</v>
       </c>
       <c r="L14" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1005,16 +1041,16 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2">
         <v>46202</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -1035,7 +1071,767 @@
         <v>16.3259</v>
       </c>
       <c r="L15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
         <v>29</v>
+      </c>
+      <c r="D16" s="2">
+        <v>46212</v>
+      </c>
+      <c r="E16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16">
+        <v>7</v>
+      </c>
+      <c r="G16">
+        <v>1.5957</v>
+      </c>
+      <c r="H16">
+        <v>0.59917</v>
+      </c>
+      <c r="I16">
+        <v>59.917</v>
+      </c>
+      <c r="J16">
+        <v>0.608249</v>
+      </c>
+      <c r="K16">
+        <v>60.8249</v>
+      </c>
+      <c r="L16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="2">
+        <v>46212</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17">
+        <v>7</v>
+      </c>
+      <c r="G17">
+        <v>3.97</v>
+      </c>
+      <c r="H17">
+        <v>0.240832</v>
+      </c>
+      <c r="I17">
+        <v>24.0832</v>
+      </c>
+      <c r="J17">
+        <v>0.237626</v>
+      </c>
+      <c r="K17">
+        <v>23.7626</v>
+      </c>
+      <c r="L17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="2">
+        <v>46212</v>
+      </c>
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18">
+        <v>7</v>
+      </c>
+      <c r="G18">
+        <v>5.9757</v>
+      </c>
+      <c r="H18">
+        <v>0.159998</v>
+      </c>
+      <c r="I18">
+        <v>15.9998</v>
+      </c>
+      <c r="J18">
+        <v>0.154125</v>
+      </c>
+      <c r="K18">
+        <v>15.4125</v>
+      </c>
+      <c r="L18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="2">
+        <v>46212</v>
+      </c>
+      <c r="E19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>1.256</v>
+      </c>
+      <c r="H19">
+        <v>0.753822</v>
+      </c>
+      <c r="I19">
+        <v>75.3822</v>
+      </c>
+      <c r="J19">
+        <v>0.768084</v>
+      </c>
+      <c r="K19">
+        <v>76.80840000000001</v>
+      </c>
+      <c r="L19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="2">
+        <v>46212</v>
+      </c>
+      <c r="E20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>3.846</v>
+      </c>
+      <c r="H20">
+        <v>0.246178</v>
+      </c>
+      <c r="I20">
+        <v>24.6178</v>
+      </c>
+      <c r="J20">
+        <v>0.231916</v>
+      </c>
+      <c r="K20">
+        <v>23.1916</v>
+      </c>
+      <c r="L20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="2">
+        <v>46213</v>
+      </c>
+      <c r="E21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21">
+        <v>7</v>
+      </c>
+      <c r="G21">
+        <v>1.6229</v>
+      </c>
+      <c r="H21">
+        <v>0.585251</v>
+      </c>
+      <c r="I21">
+        <v>58.5251</v>
+      </c>
+      <c r="J21">
+        <v>0.595148</v>
+      </c>
+      <c r="K21">
+        <v>59.5148</v>
+      </c>
+      <c r="L21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="2">
+        <v>46213</v>
+      </c>
+      <c r="E22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22">
+        <v>7</v>
+      </c>
+      <c r="G22">
+        <v>3.9129</v>
+      </c>
+      <c r="H22">
+        <v>0.242733</v>
+      </c>
+      <c r="I22">
+        <v>24.2733</v>
+      </c>
+      <c r="J22">
+        <v>0.239124</v>
+      </c>
+      <c r="K22">
+        <v>23.9124</v>
+      </c>
+      <c r="L22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="2">
+        <v>46213</v>
+      </c>
+      <c r="E23" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23">
+        <v>7</v>
+      </c>
+      <c r="G23">
+        <v>5.5214</v>
+      </c>
+      <c r="H23">
+        <v>0.172017</v>
+      </c>
+      <c r="I23">
+        <v>17.2017</v>
+      </c>
+      <c r="J23">
+        <v>0.165728</v>
+      </c>
+      <c r="K23">
+        <v>16.5728</v>
+      </c>
+      <c r="L23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="2">
+        <v>46213</v>
+      </c>
+      <c r="E24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24">
+        <v>1.3</v>
+      </c>
+      <c r="H24">
+        <v>0.726776</v>
+      </c>
+      <c r="I24">
+        <v>72.6776</v>
+      </c>
+      <c r="J24">
+        <v>0.740023</v>
+      </c>
+      <c r="K24">
+        <v>74.00230000000001</v>
+      </c>
+      <c r="L24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="2">
+        <v>46213</v>
+      </c>
+      <c r="E25" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>3.458</v>
+      </c>
+      <c r="H25">
+        <v>0.273224</v>
+      </c>
+      <c r="I25">
+        <v>27.3224</v>
+      </c>
+      <c r="J25">
+        <v>0.259977</v>
+      </c>
+      <c r="K25">
+        <v>25.9977</v>
+      </c>
+      <c r="L25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="2">
+        <v>46214</v>
+      </c>
+      <c r="E26" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26">
+        <v>4.09</v>
+      </c>
+      <c r="H26">
+        <v>0.233737</v>
+      </c>
+      <c r="I26">
+        <v>23.3737</v>
+      </c>
+      <c r="J26">
+        <v>0.230334</v>
+      </c>
+      <c r="K26">
+        <v>23.0334</v>
+      </c>
+      <c r="L26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="2">
+        <v>46214</v>
+      </c>
+      <c r="E27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27">
+        <v>7</v>
+      </c>
+      <c r="G27">
+        <v>3.72</v>
+      </c>
+      <c r="H27">
+        <v>0.256985</v>
+      </c>
+      <c r="I27">
+        <v>25.6985</v>
+      </c>
+      <c r="J27">
+        <v>0.254365</v>
+      </c>
+      <c r="K27">
+        <v>25.4365</v>
+      </c>
+      <c r="L27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="2">
+        <v>46214</v>
+      </c>
+      <c r="E28" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28">
+        <v>7</v>
+      </c>
+      <c r="G28">
+        <v>1.8771</v>
+      </c>
+      <c r="H28">
+        <v>0.509277</v>
+      </c>
+      <c r="I28">
+        <v>50.9277</v>
+      </c>
+      <c r="J28">
+        <v>0.515301</v>
+      </c>
+      <c r="K28">
+        <v>51.5301</v>
+      </c>
+      <c r="L28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" s="2">
+        <v>46214</v>
+      </c>
+      <c r="E29" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29">
+        <v>2.734</v>
+      </c>
+      <c r="H29">
+        <v>0.344993</v>
+      </c>
+      <c r="I29">
+        <v>34.4993</v>
+      </c>
+      <c r="J29">
+        <v>0.33566</v>
+      </c>
+      <c r="K29">
+        <v>33.566</v>
+      </c>
+      <c r="L29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="2">
+        <v>46214</v>
+      </c>
+      <c r="E30" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30">
+        <v>1.44</v>
+      </c>
+      <c r="H30">
+        <v>0.655007</v>
+      </c>
+      <c r="I30">
+        <v>65.50069999999999</v>
+      </c>
+      <c r="J30">
+        <v>0.66434</v>
+      </c>
+      <c r="K30">
+        <v>66.434</v>
+      </c>
+      <c r="L30" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="2">
+        <v>46215</v>
+      </c>
+      <c r="E31" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31">
+        <v>7</v>
+      </c>
+      <c r="G31">
+        <v>1.7229</v>
+      </c>
+      <c r="H31">
+        <v>0.551906</v>
+      </c>
+      <c r="I31">
+        <v>55.1906</v>
+      </c>
+      <c r="J31">
+        <v>0.560296</v>
+      </c>
+      <c r="K31">
+        <v>56.0296</v>
+      </c>
+      <c r="L31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="2">
+        <v>46215</v>
+      </c>
+      <c r="E32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32">
+        <v>7</v>
+      </c>
+      <c r="G32">
+        <v>3.5357</v>
+      </c>
+      <c r="H32">
+        <v>0.268929</v>
+      </c>
+      <c r="I32">
+        <v>26.8929</v>
+      </c>
+      <c r="J32">
+        <v>0.26641</v>
+      </c>
+      <c r="K32">
+        <v>26.641</v>
+      </c>
+      <c r="L32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="2">
+        <v>46215</v>
+      </c>
+      <c r="E33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33">
+        <v>7</v>
+      </c>
+      <c r="G33">
+        <v>5.3071</v>
+      </c>
+      <c r="H33">
+        <v>0.179165</v>
+      </c>
+      <c r="I33">
+        <v>17.9165</v>
+      </c>
+      <c r="J33">
+        <v>0.173294</v>
+      </c>
+      <c r="K33">
+        <v>17.3294</v>
+      </c>
+      <c r="L33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="2">
+        <v>46215</v>
+      </c>
+      <c r="E34" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34">
+        <v>1.33</v>
+      </c>
+      <c r="H34">
+        <v>0.711497</v>
+      </c>
+      <c r="I34">
+        <v>71.1497</v>
+      </c>
+      <c r="J34">
+        <v>0.7235009999999999</v>
+      </c>
+      <c r="K34">
+        <v>72.3501</v>
+      </c>
+      <c r="L34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="2">
+        <v>46215</v>
+      </c>
+      <c r="E35" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35">
+        <v>3.28</v>
+      </c>
+      <c r="H35">
+        <v>0.288503</v>
+      </c>
+      <c r="I35">
+        <v>28.8503</v>
+      </c>
+      <c r="J35">
+        <v>0.276499</v>
+      </c>
+      <c r="K35">
+        <v>27.6499</v>
+      </c>
+      <c r="L35" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/single_games_predictions/processed_match_predictions.xlsx
+++ b/single_games_predictions/processed_match_predictions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="44">
   <si>
     <t>Spiel_ID</t>
   </si>
@@ -76,6 +76,12 @@
     <t>arg_sch</t>
   </si>
   <si>
+    <t>fra_spa</t>
+  </si>
+  <si>
+    <t>eng_arg</t>
+  </si>
+  <si>
     <t>Deutschland</t>
   </si>
   <si>
@@ -97,6 +103,9 @@
     <t>Argentinien</t>
   </si>
   <si>
+    <t>England</t>
+  </si>
+  <si>
     <t>Curaçao</t>
   </si>
   <si>
@@ -109,9 +118,6 @@
     <t>Belgien</t>
   </si>
   <si>
-    <t>England</t>
-  </si>
-  <si>
     <t>Schweiz</t>
   </si>
   <si>
@@ -139,7 +145,7 @@
     <t>Gastteam qualifiziert</t>
   </si>
   <si>
-    <t>08.07.2026</t>
+    <t>13.07.2026</t>
   </si>
 </sst>
 </file>
@@ -501,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -547,16 +553,16 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -577,7 +583,7 @@
         <v>93.7709</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -585,16 +591,16 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -615,7 +621,7 @@
         <v>4.5869</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -623,16 +629,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -653,7 +659,7 @@
         <v>1.6422</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -661,16 +667,16 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F5">
         <v>7</v>
@@ -691,7 +697,7 @@
         <v>62.7295</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -699,16 +705,16 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -729,7 +735,7 @@
         <v>21.1517</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -737,16 +743,16 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F7">
         <v>7</v>
@@ -767,7 +773,7 @@
         <v>16.1187</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -775,16 +781,16 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -805,7 +811,7 @@
         <v>26.1603</v>
       </c>
       <c r="L8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -813,16 +819,16 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F9">
         <v>7</v>
@@ -843,7 +849,7 @@
         <v>24.0757</v>
       </c>
       <c r="L9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -851,16 +857,16 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F10">
         <v>7</v>
@@ -881,7 +887,7 @@
         <v>49.764</v>
       </c>
       <c r="L10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -889,16 +895,16 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D11" s="2">
         <v>46202</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -919,7 +925,7 @@
         <v>70.8218</v>
       </c>
       <c r="L11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -927,16 +933,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2">
         <v>46202</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F12">
         <v>7</v>
@@ -957,7 +963,7 @@
         <v>18.5747</v>
       </c>
       <c r="L12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -965,16 +971,16 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2">
         <v>46202</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F13">
         <v>7</v>
@@ -995,7 +1001,7 @@
         <v>10.6035</v>
       </c>
       <c r="L13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1003,16 +1009,16 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2">
         <v>46202</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -1033,7 +1039,7 @@
         <v>83.6741</v>
       </c>
       <c r="L14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1041,16 +1047,16 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D15" s="2">
         <v>46202</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -1071,7 +1077,7 @@
         <v>16.3259</v>
       </c>
       <c r="L15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1079,16 +1085,16 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2">
         <v>46212</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F16">
         <v>7</v>
@@ -1109,7 +1115,7 @@
         <v>60.8249</v>
       </c>
       <c r="L16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1117,16 +1123,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D17" s="2">
         <v>46212</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F17">
         <v>7</v>
@@ -1147,7 +1153,7 @@
         <v>23.7626</v>
       </c>
       <c r="L17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1155,16 +1161,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D18" s="2">
         <v>46212</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F18">
         <v>7</v>
@@ -1185,7 +1191,7 @@
         <v>15.4125</v>
       </c>
       <c r="L18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1193,16 +1199,16 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D19" s="2">
         <v>46212</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -1223,7 +1229,7 @@
         <v>76.80840000000001</v>
       </c>
       <c r="L19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1231,16 +1237,16 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D20" s="2">
         <v>46212</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -1261,7 +1267,7 @@
         <v>23.1916</v>
       </c>
       <c r="L20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1269,16 +1275,16 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D21" s="2">
         <v>46213</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F21">
         <v>7</v>
@@ -1299,7 +1305,7 @@
         <v>59.5148</v>
       </c>
       <c r="L21" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1307,16 +1313,16 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D22" s="2">
         <v>46213</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F22">
         <v>7</v>
@@ -1337,7 +1343,7 @@
         <v>23.9124</v>
       </c>
       <c r="L22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1345,16 +1351,16 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D23" s="2">
         <v>46213</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F23">
         <v>7</v>
@@ -1375,7 +1381,7 @@
         <v>16.5728</v>
       </c>
       <c r="L23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1383,16 +1389,16 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D24" s="2">
         <v>46213</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -1413,7 +1419,7 @@
         <v>74.00230000000001</v>
       </c>
       <c r="L24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1421,16 +1427,16 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D25" s="2">
         <v>46213</v>
       </c>
       <c r="E25" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -1451,7 +1457,7 @@
         <v>25.9977</v>
       </c>
       <c r="L25" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1459,16 +1465,16 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D26" s="2">
         <v>46214</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F26">
         <v>7</v>
@@ -1489,7 +1495,7 @@
         <v>23.0334</v>
       </c>
       <c r="L26" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1497,16 +1503,16 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D27" s="2">
         <v>46214</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F27">
         <v>7</v>
@@ -1527,7 +1533,7 @@
         <v>25.4365</v>
       </c>
       <c r="L27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1535,16 +1541,16 @@
         <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D28" s="2">
         <v>46214</v>
       </c>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F28">
         <v>7</v>
@@ -1565,7 +1571,7 @@
         <v>51.5301</v>
       </c>
       <c r="L28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1573,16 +1579,16 @@
         <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2">
         <v>46214</v>
       </c>
       <c r="E29" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -1603,7 +1609,7 @@
         <v>33.566</v>
       </c>
       <c r="L29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1611,16 +1617,16 @@
         <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D30" s="2">
         <v>46214</v>
       </c>
       <c r="E30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F30">
         <v>5</v>
@@ -1641,7 +1647,7 @@
         <v>66.434</v>
       </c>
       <c r="L30" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1649,16 +1655,16 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D31" s="2">
         <v>46215</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F31">
         <v>7</v>
@@ -1679,7 +1685,7 @@
         <v>56.0296</v>
       </c>
       <c r="L31" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1687,16 +1693,16 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D32" s="2">
         <v>46215</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F32">
         <v>7</v>
@@ -1717,7 +1723,7 @@
         <v>26.641</v>
       </c>
       <c r="L32" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1725,16 +1731,16 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D33" s="2">
         <v>46215</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F33">
         <v>7</v>
@@ -1755,7 +1761,7 @@
         <v>17.3294</v>
       </c>
       <c r="L33" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -1763,16 +1769,16 @@
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D34" s="2">
         <v>46215</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F34">
         <v>5</v>
@@ -1793,7 +1799,7 @@
         <v>72.3501</v>
       </c>
       <c r="L34" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -1801,16 +1807,16 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D35" s="2">
         <v>46215</v>
       </c>
       <c r="E35" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F35">
         <v>5</v>
@@ -1831,7 +1837,387 @@
         <v>27.6499</v>
       </c>
       <c r="L35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="2">
+        <v>46217</v>
+      </c>
+      <c r="E36" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36">
+        <v>7</v>
+      </c>
+      <c r="G36">
+        <v>2.3271</v>
+      </c>
+      <c r="H36">
+        <v>0.40842</v>
+      </c>
+      <c r="I36">
+        <v>40.842</v>
+      </c>
+      <c r="J36">
+        <v>0.411324</v>
+      </c>
+      <c r="K36">
+        <v>41.1324</v>
+      </c>
+      <c r="L36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="2">
+        <v>46217</v>
+      </c>
+      <c r="E37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37">
+        <v>7</v>
+      </c>
+      <c r="G37">
+        <v>3.1571</v>
+      </c>
+      <c r="H37">
+        <v>0.301048</v>
+      </c>
+      <c r="I37">
+        <v>30.1048</v>
+      </c>
+      <c r="J37">
+        <v>0.299799</v>
+      </c>
+      <c r="K37">
+        <v>29.9799</v>
+      </c>
+      <c r="L37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="2">
+        <v>46217</v>
+      </c>
+      <c r="E38" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38">
+        <v>7</v>
+      </c>
+      <c r="G38">
+        <v>3.2714</v>
+      </c>
+      <c r="H38">
+        <v>0.290531</v>
+      </c>
+      <c r="I38">
+        <v>29.0531</v>
+      </c>
+      <c r="J38">
+        <v>0.288878</v>
+      </c>
+      <c r="K38">
+        <v>28.8878</v>
+      </c>
+      <c r="L38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="2">
+        <v>46217</v>
+      </c>
+      <c r="E39" t="s">
         <v>41</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39">
+        <v>1.648</v>
+      </c>
+      <c r="H39">
+        <v>0.5774359999999999</v>
+      </c>
+      <c r="I39">
+        <v>57.7436</v>
+      </c>
+      <c r="J39">
+        <v>0.581373</v>
+      </c>
+      <c r="K39">
+        <v>58.1373</v>
+      </c>
+      <c r="L39" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="2">
+        <v>46217</v>
+      </c>
+      <c r="E40" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40">
+        <v>2.252</v>
+      </c>
+      <c r="H40">
+        <v>0.422564</v>
+      </c>
+      <c r="I40">
+        <v>42.2564</v>
+      </c>
+      <c r="J40">
+        <v>0.418627</v>
+      </c>
+      <c r="K40">
+        <v>41.8627</v>
+      </c>
+      <c r="L40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="2">
+        <v>46218</v>
+      </c>
+      <c r="E41" t="s">
+        <v>38</v>
+      </c>
+      <c r="F41">
+        <v>7</v>
+      </c>
+      <c r="G41">
+        <v>2.6214</v>
+      </c>
+      <c r="H41">
+        <v>0.362403</v>
+      </c>
+      <c r="I41">
+        <v>36.2403</v>
+      </c>
+      <c r="J41">
+        <v>0.363536</v>
+      </c>
+      <c r="K41">
+        <v>36.3536</v>
+      </c>
+      <c r="L41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="2">
+        <v>46218</v>
+      </c>
+      <c r="E42" t="s">
+        <v>39</v>
+      </c>
+      <c r="F42">
+        <v>7</v>
+      </c>
+      <c r="G42">
+        <v>2.9729</v>
+      </c>
+      <c r="H42">
+        <v>0.319563</v>
+      </c>
+      <c r="I42">
+        <v>31.9563</v>
+      </c>
+      <c r="J42">
+        <v>0.319026</v>
+      </c>
+      <c r="K42">
+        <v>31.9026</v>
+      </c>
+      <c r="L42" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" s="2">
+        <v>46218</v>
+      </c>
+      <c r="E43" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43">
+        <v>7</v>
+      </c>
+      <c r="G43">
+        <v>2.9871</v>
+      </c>
+      <c r="H43">
+        <v>0.318034</v>
+      </c>
+      <c r="I43">
+        <v>31.8034</v>
+      </c>
+      <c r="J43">
+        <v>0.317438</v>
+      </c>
+      <c r="K43">
+        <v>31.7438</v>
+      </c>
+      <c r="L43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="2">
+        <v>46218</v>
+      </c>
+      <c r="E44" t="s">
+        <v>41</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="G44">
+        <v>1.77</v>
+      </c>
+      <c r="H44">
+        <v>0.535433</v>
+      </c>
+      <c r="I44">
+        <v>53.5433</v>
+      </c>
+      <c r="J44">
+        <v>0.537388</v>
+      </c>
+      <c r="K44">
+        <v>53.7388</v>
+      </c>
+      <c r="L44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="2">
+        <v>46218</v>
+      </c>
+      <c r="E45" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+      <c r="G45">
+        <v>2.04</v>
+      </c>
+      <c r="H45">
+        <v>0.464567</v>
+      </c>
+      <c r="I45">
+        <v>46.4567</v>
+      </c>
+      <c r="J45">
+        <v>0.462612</v>
+      </c>
+      <c r="K45">
+        <v>46.2612</v>
+      </c>
+      <c r="L45" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/single_games_predictions/processed_match_predictions.xlsx
+++ b/single_games_predictions/processed_match_predictions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="46">
   <si>
     <t>Spiel_ID</t>
   </si>
@@ -82,6 +82,12 @@
     <t>eng_arg</t>
   </si>
   <si>
+    <t>fra_eng</t>
+  </si>
+  <si>
+    <t>spa_arg</t>
+  </si>
+  <si>
     <t>Deutschland</t>
   </si>
   <si>
@@ -145,7 +151,7 @@
     <t>Gastteam qualifiziert</t>
   </si>
   <si>
-    <t>13.07.2026</t>
+    <t>16.07.2026</t>
   </si>
 </sst>
 </file>
@@ -507,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -553,16 +559,16 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -583,7 +589,7 @@
         <v>93.7709</v>
       </c>
       <c r="L2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -591,16 +597,16 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -621,7 +627,7 @@
         <v>4.5869</v>
       </c>
       <c r="L3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -629,16 +635,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -659,7 +665,7 @@
         <v>1.6422</v>
       </c>
       <c r="L4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -667,16 +673,16 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>7</v>
@@ -697,7 +703,7 @@
         <v>62.7295</v>
       </c>
       <c r="L5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -705,16 +711,16 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -735,7 +741,7 @@
         <v>21.1517</v>
       </c>
       <c r="L6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -743,16 +749,16 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F7">
         <v>7</v>
@@ -773,7 +779,7 @@
         <v>16.1187</v>
       </c>
       <c r="L7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -781,16 +787,16 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -811,7 +817,7 @@
         <v>26.1603</v>
       </c>
       <c r="L8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -819,16 +825,16 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F9">
         <v>7</v>
@@ -849,7 +855,7 @@
         <v>24.0757</v>
       </c>
       <c r="L9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -857,16 +863,16 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F10">
         <v>7</v>
@@ -887,7 +893,7 @@
         <v>49.764</v>
       </c>
       <c r="L10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -895,16 +901,16 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" s="2">
         <v>46202</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -925,7 +931,7 @@
         <v>70.8218</v>
       </c>
       <c r="L11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -933,16 +939,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D12" s="2">
         <v>46202</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F12">
         <v>7</v>
@@ -963,7 +969,7 @@
         <v>18.5747</v>
       </c>
       <c r="L12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -971,16 +977,16 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D13" s="2">
         <v>46202</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F13">
         <v>7</v>
@@ -1001,7 +1007,7 @@
         <v>10.6035</v>
       </c>
       <c r="L13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1009,16 +1015,16 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D14" s="2">
         <v>46202</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -1039,7 +1045,7 @@
         <v>83.6741</v>
       </c>
       <c r="L14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1047,16 +1053,16 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15" s="2">
         <v>46202</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -1077,7 +1083,7 @@
         <v>16.3259</v>
       </c>
       <c r="L15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1085,16 +1091,16 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" s="2">
         <v>46212</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F16">
         <v>7</v>
@@ -1115,7 +1121,7 @@
         <v>60.8249</v>
       </c>
       <c r="L16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1123,16 +1129,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" s="2">
         <v>46212</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F17">
         <v>7</v>
@@ -1153,7 +1159,7 @@
         <v>23.7626</v>
       </c>
       <c r="L17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1161,16 +1167,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" s="2">
         <v>46212</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F18">
         <v>7</v>
@@ -1191,7 +1197,7 @@
         <v>15.4125</v>
       </c>
       <c r="L18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1199,16 +1205,16 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D19" s="2">
         <v>46212</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -1229,7 +1235,7 @@
         <v>76.80840000000001</v>
       </c>
       <c r="L19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1237,16 +1243,16 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D20" s="2">
         <v>46212</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -1267,7 +1273,7 @@
         <v>23.1916</v>
       </c>
       <c r="L20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1275,16 +1281,16 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D21" s="2">
         <v>46213</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F21">
         <v>7</v>
@@ -1305,7 +1311,7 @@
         <v>59.5148</v>
       </c>
       <c r="L21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1313,16 +1319,16 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D22" s="2">
         <v>46213</v>
       </c>
       <c r="E22" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F22">
         <v>7</v>
@@ -1343,7 +1349,7 @@
         <v>23.9124</v>
       </c>
       <c r="L22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1351,16 +1357,16 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D23" s="2">
         <v>46213</v>
       </c>
       <c r="E23" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F23">
         <v>7</v>
@@ -1381,7 +1387,7 @@
         <v>16.5728</v>
       </c>
       <c r="L23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1389,16 +1395,16 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D24" s="2">
         <v>46213</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -1419,7 +1425,7 @@
         <v>74.00230000000001</v>
       </c>
       <c r="L24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1427,16 +1433,16 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D25" s="2">
         <v>46213</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -1457,7 +1463,7 @@
         <v>25.9977</v>
       </c>
       <c r="L25" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1465,16 +1471,16 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D26" s="2">
         <v>46214</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F26">
         <v>7</v>
@@ -1495,7 +1501,7 @@
         <v>23.0334</v>
       </c>
       <c r="L26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1503,16 +1509,16 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D27" s="2">
         <v>46214</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F27">
         <v>7</v>
@@ -1533,7 +1539,7 @@
         <v>25.4365</v>
       </c>
       <c r="L27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1541,16 +1547,16 @@
         <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D28" s="2">
         <v>46214</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F28">
         <v>7</v>
@@ -1571,7 +1577,7 @@
         <v>51.5301</v>
       </c>
       <c r="L28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1579,16 +1585,16 @@
         <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D29" s="2">
         <v>46214</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -1609,7 +1615,7 @@
         <v>33.566</v>
       </c>
       <c r="L29" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1617,16 +1623,16 @@
         <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D30" s="2">
         <v>46214</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F30">
         <v>5</v>
@@ -1647,7 +1653,7 @@
         <v>66.434</v>
       </c>
       <c r="L30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1655,16 +1661,16 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D31" s="2">
         <v>46215</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F31">
         <v>7</v>
@@ -1685,7 +1691,7 @@
         <v>56.0296</v>
       </c>
       <c r="L31" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1693,16 +1699,16 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D32" s="2">
         <v>46215</v>
       </c>
       <c r="E32" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F32">
         <v>7</v>
@@ -1723,7 +1729,7 @@
         <v>26.641</v>
       </c>
       <c r="L32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1731,16 +1737,16 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D33" s="2">
         <v>46215</v>
       </c>
       <c r="E33" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F33">
         <v>7</v>
@@ -1761,7 +1767,7 @@
         <v>17.3294</v>
       </c>
       <c r="L33" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -1769,16 +1775,16 @@
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D34" s="2">
         <v>46215</v>
       </c>
       <c r="E34" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F34">
         <v>5</v>
@@ -1799,7 +1805,7 @@
         <v>72.3501</v>
       </c>
       <c r="L34" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -1807,16 +1813,16 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D35" s="2">
         <v>46215</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F35">
         <v>5</v>
@@ -1837,7 +1843,7 @@
         <v>27.6499</v>
       </c>
       <c r="L35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -1845,16 +1851,16 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D36" s="2">
         <v>46217</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F36">
         <v>7</v>
@@ -1875,7 +1881,7 @@
         <v>41.1324</v>
       </c>
       <c r="L36" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -1883,16 +1889,16 @@
         <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D37" s="2">
         <v>46217</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F37">
         <v>7</v>
@@ -1913,7 +1919,7 @@
         <v>29.9799</v>
       </c>
       <c r="L37" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -1921,16 +1927,16 @@
         <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D38" s="2">
         <v>46217</v>
       </c>
       <c r="E38" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F38">
         <v>7</v>
@@ -1951,7 +1957,7 @@
         <v>28.8878</v>
       </c>
       <c r="L38" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -1959,16 +1965,16 @@
         <v>20</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D39" s="2">
         <v>46217</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F39">
         <v>5</v>
@@ -1989,7 +1995,7 @@
         <v>58.1373</v>
       </c>
       <c r="L39" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -1997,16 +2003,16 @@
         <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D40" s="2">
         <v>46217</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F40">
         <v>5</v>
@@ -2027,7 +2033,7 @@
         <v>41.8627</v>
       </c>
       <c r="L40" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2035,16 +2041,16 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D41" s="2">
         <v>46218</v>
       </c>
       <c r="E41" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F41">
         <v>7</v>
@@ -2065,7 +2071,7 @@
         <v>36.3536</v>
       </c>
       <c r="L41" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2073,16 +2079,16 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D42" s="2">
         <v>46218</v>
       </c>
       <c r="E42" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F42">
         <v>7</v>
@@ -2103,7 +2109,7 @@
         <v>31.9026</v>
       </c>
       <c r="L42" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2111,16 +2117,16 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D43" s="2">
         <v>46218</v>
       </c>
       <c r="E43" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F43">
         <v>7</v>
@@ -2141,7 +2147,7 @@
         <v>31.7438</v>
       </c>
       <c r="L43" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2149,16 +2155,16 @@
         <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D44" s="2">
         <v>46218</v>
       </c>
       <c r="E44" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F44">
         <v>5</v>
@@ -2179,7 +2185,7 @@
         <v>53.7388</v>
       </c>
       <c r="L44" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2187,16 +2193,16 @@
         <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D45" s="2">
         <v>46218</v>
       </c>
       <c r="E45" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F45">
         <v>5</v>
@@ -2217,7 +2223,235 @@
         <v>46.2612</v>
       </c>
       <c r="L45" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46" s="2">
+        <v>46221</v>
+      </c>
+      <c r="E46" t="s">
+        <v>40</v>
+      </c>
+      <c r="F46">
+        <v>7</v>
+      </c>
+      <c r="G46">
+        <v>1.9086</v>
+      </c>
+      <c r="H46">
+        <v>0.498309</v>
+      </c>
+      <c r="I46">
+        <v>49.8309</v>
+      </c>
+      <c r="J46">
+        <v>0.504616</v>
+      </c>
+      <c r="K46">
+        <v>50.4616</v>
+      </c>
+      <c r="L46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47" s="2">
+        <v>46221</v>
+      </c>
+      <c r="E47" t="s">
+        <v>41</v>
+      </c>
+      <c r="F47">
+        <v>7</v>
+      </c>
+      <c r="G47">
+        <v>3.7843</v>
+      </c>
+      <c r="H47">
+        <v>0.251318</v>
+      </c>
+      <c r="I47">
+        <v>25.1318</v>
+      </c>
+      <c r="J47">
+        <v>0.248182</v>
+      </c>
+      <c r="K47">
+        <v>24.8182</v>
+      </c>
+      <c r="L47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48" s="2">
+        <v>46221</v>
+      </c>
+      <c r="E48" t="s">
+        <v>42</v>
+      </c>
+      <c r="F48">
+        <v>7</v>
+      </c>
+      <c r="G48">
+        <v>3.7986</v>
+      </c>
+      <c r="H48">
+        <v>0.250373</v>
+      </c>
+      <c r="I48">
+        <v>25.0373</v>
+      </c>
+      <c r="J48">
+        <v>0.247202</v>
+      </c>
+      <c r="K48">
+        <v>24.7202</v>
+      </c>
+      <c r="L48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" s="2">
+        <v>46222</v>
+      </c>
+      <c r="E49" t="s">
+        <v>40</v>
+      </c>
+      <c r="F49">
+        <v>7</v>
+      </c>
+      <c r="G49">
+        <v>2.2929</v>
+      </c>
+      <c r="H49">
+        <v>0.413572</v>
+      </c>
+      <c r="I49">
+        <v>41.3572</v>
+      </c>
+      <c r="J49">
+        <v>0.416817</v>
+      </c>
+      <c r="K49">
+        <v>41.6817</v>
+      </c>
+      <c r="L49" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="2">
+        <v>46222</v>
+      </c>
+      <c r="E50" t="s">
+        <v>41</v>
+      </c>
+      <c r="F50">
+        <v>7</v>
+      </c>
+      <c r="G50">
+        <v>3.0014</v>
+      </c>
+      <c r="H50">
+        <v>0.315937</v>
+      </c>
+      <c r="I50">
+        <v>31.5937</v>
+      </c>
+      <c r="J50">
+        <v>0.315227</v>
+      </c>
+      <c r="K50">
+        <v>31.5227</v>
+      </c>
+      <c r="L50" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="2">
+        <v>46222</v>
+      </c>
+      <c r="E51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51">
+        <v>7</v>
+      </c>
+      <c r="G51">
+        <v>3.5057</v>
+      </c>
+      <c r="H51">
+        <v>0.270491</v>
+      </c>
+      <c r="I51">
+        <v>27.0491</v>
+      </c>
+      <c r="J51">
+        <v>0.267956</v>
+      </c>
+      <c r="K51">
+        <v>26.7956</v>
+      </c>
+      <c r="L51" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
